--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.5582092465167</v>
+        <v>8.540709002558964</v>
       </c>
       <c r="D2" t="n">
-        <v>32.76500044286524</v>
+        <v>5.324312571965602</v>
       </c>
       <c r="E2" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F2" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.63781081381424</v>
+        <v>3.841144257244814</v>
       </c>
       <c r="D3" t="n">
-        <v>4.765814580098613</v>
+        <v>0.7744448692660247</v>
       </c>
       <c r="E3" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F3" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.06890604580683</v>
+        <v>8.623697232443611</v>
       </c>
       <c r="D4" t="n">
-        <v>53.62833997091391</v>
+        <v>8.714605245273511</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F4" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.31785140042495</v>
+        <v>7.526650852569055</v>
       </c>
       <c r="D5" t="n">
-        <v>47.60912973686893</v>
+        <v>7.736483582241202</v>
       </c>
       <c r="E5" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F5" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.93561054837303</v>
+        <v>4.702036714110617</v>
       </c>
       <c r="D6" t="n">
-        <v>30.10969180270138</v>
+        <v>4.892824917938975</v>
       </c>
       <c r="E6" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F6" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.67556611637363</v>
+        <v>7.747279493910715</v>
       </c>
       <c r="D7" t="n">
-        <v>47.33789271131113</v>
+        <v>7.692407565588059</v>
       </c>
       <c r="E7" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F7" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.66589880544032</v>
+        <v>3.358208555884052</v>
       </c>
       <c r="D8" t="n">
-        <v>20.70005130777819</v>
+        <v>3.363758337513957</v>
       </c>
       <c r="E8" t="n">
-        <v>13.00549776172074</v>
+        <v>2.113393386279621</v>
       </c>
       <c r="F8" t="n">
-        <v>16.01962006235024</v>
+        <v>2.603188260131914</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
